--- a/CNA-Recert-Course/ContentV2/xlsx/CNA_RECERT_CONTENTV2_MASTER.xlsx
+++ b/CNA-Recert-Course/ContentV2/xlsx/CNA_RECERT_CONTENTV2_MASTER.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modules'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Modules'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cards'!$A$1:$L$339</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Narration'!$A$1:$H$339</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Media Placeholders'!$A$1:$G$339</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Runtime Summary'!$A$1:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Runtime Summary'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,30 +460,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Declared min</t>
+          <t>Narration min</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Reading min</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Interaction min</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Assessment min (excl.)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Lessons</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cards</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Time-model status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SME Flag</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Compliance Flag</t>
         </is>
@@ -507,25 +522,34 @@
         <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H2" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
         <v>20</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>authored</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>None identified</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Compliance/legal/CDPH review required before production.</t>
         </is>
@@ -549,25 +573,34 @@
         <v>90</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>19.5</v>
       </c>
       <c r="F3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>33</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>sme-review</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>authored</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Module 1 infection-control content requires SME/source review (no dedicated NATP 10-17 source module).</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Compliance review required; no dedicated NATP 10-17 infection-control source in uploaded set.</t>
         </is>
@@ -591,25 +624,34 @@
         <v>120</v>
       </c>
       <c r="E4" t="n">
-        <v>120</v>
+        <v>32.7</v>
       </c>
       <c r="F4" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>55</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>authored-partial</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>None identified</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Compliance/legal/CDPH review required before production.</t>
         </is>
@@ -633,25 +675,34 @@
         <v>120</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>20.5</v>
       </c>
       <c r="F5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>37</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>source-repair</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Module 3 placement and sensitive end-of-life/trauma-informed content should receive SME review.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Canonical Module 3 file is incomplete after Screen 3.2.3; source repair required before production.</t>
         </is>
@@ -675,25 +726,34 @@
         <v>120</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>31.4</v>
       </c>
       <c r="F6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>55</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>authored-partial</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>None identified</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Compliance review required; no clinical competency or clinical-hour claim.</t>
         </is>
@@ -717,25 +777,34 @@
         <v>120</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>28.6</v>
       </c>
       <c r="F7" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>49</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>sme-review</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>authored-partial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Skin integrity / pressure injury content requires SME/source review.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Compliance review required; keep CNA role as observe/report, not independent staging/treatment.</t>
         </is>
@@ -759,25 +828,34 @@
         <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>43</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>authored-partial</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>None identified</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Compliance review required; PHI/no-upload and CNA scope guardrails apply.</t>
         </is>
@@ -795,38 +873,47 @@
         </is>
       </c>
       <c r="C9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>46</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>authored-partial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>None identified</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Affidavit/certificate wording requires legal/compliance/CDPH or owner approval; production certificate disabled.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -48277,7 +48364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48415,11 +48502,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>instructional_minutes_total</t>
+          <t>required_theory_instructional_minutes_total</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>570</v>
+        <v>720</v>
       </c>
     </row>
     <row r="15">
@@ -48439,35 +48526,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>generated_at</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-01T22:01:28+00:00</t>
-        </is>
+          <t>narration_model_minutes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>191.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>content_depth_gap_minutes</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-01T23:54:23+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>audio_production</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Not authorized - transcripts/manifest only</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B18"/>
+  <autoFilter ref="A1:B20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/CNA-Recert-Course/ContentV2/xlsx/CNA_RECERT_CONTENTV2_MASTER.xlsx
+++ b/CNA-Recert-Course/ContentV2/xlsx/CNA_RECERT_CONTENTV2_MASTER.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>authored</t>
+          <t>under-depth</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>authored-partial</t>
+          <t>under-depth</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>authored-partial</t>
+          <t>under-depth</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>authored-partial</t>
+          <t>under-depth</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>authored-partial</t>
+          <t>under-depth</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-02T00:31:57+00:00</t>
+          <t>2026-06-02T01:57:05+00:00</t>
         </is>
       </c>
     </row>
